--- a/artfynd/A 21196-2024 artfynd.xlsx
+++ b/artfynd/A 21196-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +801,107 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128962425</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91508</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sursvavägen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>601715</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6723714</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lars o Maria Westerman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars o Maria Westerman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21196-2024 artfynd.xlsx
+++ b/artfynd/A 21196-2024 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128962425</v>
       </c>
       <c r="B3" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21196-2024 artfynd.xlsx
+++ b/artfynd/A 21196-2024 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128962425</v>
       </c>
       <c r="B3" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21196-2024 artfynd.xlsx
+++ b/artfynd/A 21196-2024 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128962425</v>
       </c>
       <c r="B3" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21196-2024 artfynd.xlsx
+++ b/artfynd/A 21196-2024 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128962425</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21196-2024 artfynd.xlsx
+++ b/artfynd/A 21196-2024 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128962425</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21196-2024 artfynd.xlsx
+++ b/artfynd/A 21196-2024 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128962425</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21196-2024 artfynd.xlsx
+++ b/artfynd/A 21196-2024 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128962425</v>
       </c>
       <c r="B3" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21196-2024 artfynd.xlsx
+++ b/artfynd/A 21196-2024 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128962425</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21196-2024 artfynd.xlsx
+++ b/artfynd/A 21196-2024 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128962425</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21196-2024 artfynd.xlsx
+++ b/artfynd/A 21196-2024 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128962425</v>
       </c>
       <c r="B3" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21196-2024 artfynd.xlsx
+++ b/artfynd/A 21196-2024 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>128962425</v>
       </c>
       <c r="B3" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21196-2024 artfynd.xlsx
+++ b/artfynd/A 21196-2024 artfynd.xlsx
@@ -675,65 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106868234</v>
+        <v>128962425</v>
       </c>
       <c r="B2" t="n">
-        <v>57234</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100136</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sursvavägen öst, Gstr</t>
+          <t>Sursvavägen, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601810</v>
+        <v>601715</v>
       </c>
       <c r="R2" t="n">
-        <v>6723689</v>
+        <v>6723714</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Satt och spanade längs Sursvavägen ca 100m väster om markerad lokal.</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,69 +757,79 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Åberg</t>
+          <t>Lars o Maria Westerman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Åberg</t>
+          <t>Lars o Maria Westerman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128962425</v>
+        <v>106868234</v>
       </c>
       <c r="B3" t="n">
-        <v>91550</v>
+        <v>57813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100136</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sursvavägen, Gstr</t>
+          <t>Sursvavägen öst, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601715</v>
+        <v>601810</v>
       </c>
       <c r="R3" t="n">
-        <v>6723714</v>
+        <v>6723689</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,12 +853,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2023-01-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2023-01-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Satt och spanade längs Sursvavägen ca 100m väster om markerad lokal.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,19 +882,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars o Maria Westerman</t>
+          <t>Thomas Åberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars o Maria Westerman</t>
+          <t>Thomas Åberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 21196-2024 artfynd.xlsx
+++ b/artfynd/A 21196-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128962425</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,8 +907,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106868234</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>